--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T20:14:11+00:00</t>
+    <t>2026-09-14T10:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1688,7 +1688,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>Nachweis oder Ausschluss des im Code benannten Ziels — auch dann, wenn er kulturell erfolgte: Eine zielgerichtete Kultur berichtet 'Detected' oder 'Not detected' und nicht 'Organism growth', weil die Kultur schon im Untersuchungscode steht (Ballotfrage 7). Ein grenzwertiger Befund wird als 'Weakly positive' oder 'Equivocal result' berichtet — das ist eine Aussage und gehört deshalb hierher. Ein unbestimmbares Ergebnis, bei dem die Untersuchung gar keine verwertbare Aussage liefert (z. B. inhibierte PCR), wird dagegen über dataAbsentReason abgebildet.</t>
+    <t>Nachweis oder Ausschluss des im Code benannten Ziels — auch dann, wenn er kulturell erfolgte: Eine zielgerichtete Kultur berichtet 'Detected' oder 'Not detected' und nicht 'Organism growth', weil die Kultur schon im Untersuchungscode steht (Ballotfrage 6). Ein grenzwertiger Befund wird als 'Weakly positive' oder 'Equivocal result' berichtet — das ist eine Aussage und gehört deshalb hierher. Ein unbestimmbares Ergebnis, bei dem die Untersuchung gar keine verwertbare Aussage liefert (z. B. inhibierte PCR), wird dagegen über dataAbsentReason abgebildet.</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T10:47:12+00:00</t>
+    <t>2026-09-14T11:35:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:35:30+00:00</t>
+    <t>2026-09-14T12:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:58:37+00:00</t>
+    <t>2026-09-14T13:24:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:24:58+00:00</t>
+    <t>2026-09-14T13:41:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:41:44+00:00</t>
+    <t>2026-09-14T14:16:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
